--- a/jpcore-r4/feature/fix-tx-error/ValueSet-jp-observation-electrocardiogram-duration-vs.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/ValueSet-jp-observation-electrocardiogram-duration-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrogardiogramDuration_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramDuration_VS</t>
   </si>
   <si>
     <t>Version</t>
@@ -36,13 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>JP_ObservationElectrogardiogramDuration_VS</t>
+    <t>JP_ObservationElectrocardiogramDuration_VS</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>JP Core Observation ElectroCardioGram Duration ValueSet</t>
+    <t>JP Core Observation Electrocardiogram Duration ValueSet</t>
   </si>
   <si>
     <t>Status</t>
@@ -114,7 +114,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationElectrogardiogramDuration_CS</t>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationElectrocardiogramDuration_CS</t>
   </si>
 </sst>
 </file>
